--- a/backend/local_storage/default/daily_work.xlsx
+++ b/backend/local_storage/default/daily_work.xlsx
@@ -505,7 +505,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -541,7 +541,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
